--- a/Result/profitability/7805.xlsx
+++ b/Result/profitability/7805.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AM13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,10 +1487,10 @@
         <v>197</v>
       </c>
       <c r="L9" t="n">
-        <v>6.52</v>
+        <v>6.56</v>
       </c>
       <c r="M9" t="n">
-        <v>5.79125</v>
+        <v>5.79625</v>
       </c>
       <c r="N9" t="n">
         <v>58.0525</v>
@@ -1520,10 +1520,10 @@
         <v>114.2</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.220000000000001</v>
+        <v>-5.180000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.444633730834753</v>
+        <v>-0.4412265758091993</v>
       </c>
       <c r="Y9" t="n">
         <v>-2.420000000000002</v>
@@ -1532,10 +1532,10 @@
         <v>-0.04333810888252154</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AC9" t="n">
         <v>-3.439999999999998</v>
@@ -1617,7 +1617,7 @@
         <v>12.65</v>
       </c>
       <c r="M10" t="n">
-        <v>6.788749999999999</v>
+        <v>6.793749999999999</v>
       </c>
       <c r="N10" t="n">
         <v>57.43125</v>
@@ -1647,10 +1647,10 @@
         <v>114.3</v>
       </c>
       <c r="W10" t="n">
-        <v>6.130000000000001</v>
+        <v>6.090000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9401840490797548</v>
+        <v>0.9283536585365855</v>
       </c>
       <c r="Y10" t="n">
         <v>6.100000000000001</v>
@@ -1744,7 +1744,7 @@
         <v>13.84</v>
       </c>
       <c r="M11" t="n">
-        <v>7.9575</v>
+        <v>7.9625</v>
       </c>
       <c r="N11" t="n">
         <v>56.9975</v>
@@ -1871,7 +1871,7 @@
         <v>12.96</v>
       </c>
       <c r="M12" t="n">
-        <v>9.22875</v>
+        <v>9.233750000000001</v>
       </c>
       <c r="N12" t="n">
         <v>57.17</v>
@@ -1952,6 +1952,133 @@
       </c>
       <c r="AM12" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7805</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1681</v>
+      </c>
+      <c r="D13" t="n">
+        <v>697</v>
+      </c>
+      <c r="E13" t="n">
+        <v>984</v>
+      </c>
+      <c r="F13" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="G13" t="n">
+        <v>432</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>25.69%</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>449</v>
+      </c>
+      <c r="K13" t="n">
+        <v>340</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10.26625</v>
+      </c>
+      <c r="N13" t="n">
+        <v>57.37875</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-2.700000000000001</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.2083333333333334</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-2.759999999999998</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.04503181595692607</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5640243902439026</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.109999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.09565705728191687</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
